--- a/artifacts/关键标准答案.xlsx
+++ b/artifacts/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Re9b09924ec084f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R49183bc23ce045cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rffb5ea86f2e04d0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R9a3c381a0b604427"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R5fc8d831ab774597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R9174fe842e7d48f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R4039336f96fb41c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Ra25464dc87ed4df9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rf1a641bf35bc480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R48759c5af0bc4b00"/>
   </x:sheets>
 </x:workbook>
 </file>
